--- a/src/nodes/HPC/compressor_stage_5_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_5_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-14.944835058430154</v>
+        <v>-14.951666171112036</v>
       </c>
       <c r="B1">
-        <v>7.4944492410017158</v>
+        <v>7.4808116576517367</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-13.639205627461127</v>
+        <v>-13.674732013061034</v>
       </c>
       <c r="B2">
-        <v>7.865139211857473</v>
+        <v>7.8060301581682285</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-12.603248799155162</v>
+        <v>-12.649439283113255</v>
       </c>
       <c r="B3">
-        <v>7.7929768826578547</v>
+        <v>7.7171569139215821</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-11.608978316210438</v>
+        <v>-11.663317969129103</v>
       </c>
       <c r="B4">
-        <v>7.6523578628570386</v>
+        <v>7.563824649141309</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-10.643705420726555</v>
+        <v>-10.70454136107869</v>
       </c>
       <c r="B5">
-        <v>7.4641194402089246</v>
+        <v>7.3654949565706751</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-9.7022477940323242</v>
+        <v>-9.7682783585492459</v>
       </c>
       <c r="B6">
-        <v>7.2367719406438953</v>
+        <v>7.13011771478941</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-8.7816420117289216</v>
+        <v>-8.8517658511113879</v>
       </c>
       <c r="B7">
-        <v>6.9751818552259355</v>
+        <v>6.8622397952220764</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-7.8801404107590178</v>
+        <v>-7.9533738005423054</v>
       </c>
       <c r="B8">
-        <v>6.6822191699937212</v>
+        <v>6.56454352794762</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-6.9950201077456962</v>
+        <v>-7.07056346268107</v>
       </c>
       <c r="B9">
-        <v>6.3623553631558156</v>
+        <v>6.2412065756308719</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.1233430136168989</v>
+        <v>-6.20059560111948</v>
       </c>
       <c r="B10">
-        <v>6.0204153204828756</v>
+        <v>5.8967365234979132</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.26228543683965</v>
+        <v>-5.340837716398446</v>
       </c>
       <c r="B11">
-        <v>5.6610360658241063</v>
+        <v>5.5354653144339734</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.4103358630106593</v>
+        <v>-4.48988023407821</v>
       </c>
       <c r="B12">
-        <v>5.2866997854433464</v>
+        <v>5.159712491542642</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.5711170887063011</v>
+        <v>-3.6510985428472038</v>
       </c>
       <c r="B13">
-        <v>4.8914571771844413</v>
+        <v>4.7639236411417949</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.7467931095785771</v>
+        <v>-2.8265085865290271</v>
       </c>
       <c r="B14">
-        <v>4.4717545598712727</v>
+        <v>4.3447814012948429</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.9285584066023431</v>
+        <v>-2.0079035663597495</v>
       </c>
       <c r="B15">
-        <v>4.04205222466785</v>
+        <v>3.9157905738330614</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.1083366209022463</v>
+        <v>-1.187756266834864</v>
       </c>
       <c r="B16">
-        <v>3.6156130468855943</v>
+        <v>3.4893376637328708</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-0.29193754887919204</v>
+        <v>-0.37148054807501613</v>
       </c>
       <c r="B17">
-        <v>3.182896266085395</v>
+        <v>3.056513824783353</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>0.51313416850439442</v>
+        <v>0.43393017587642996</v>
       </c>
       <c r="B18">
-        <v>2.7315778735304543</v>
+        <v>2.6058109557752158</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1.3064806673163474</v>
+        <v>1.2281053509104862</v>
       </c>
       <c r="B19">
-        <v>2.2610045030436705</v>
+        <v>2.1366192866929303</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.0894807778820663</v>
+        <v>2.012330137901754</v>
       </c>
       <c r="B20">
-        <v>1.7734404490878772</v>
+        <v>1.6510536303194121</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.8635133305269416</v>
+        <v>2.7878896977248275</v>
       </c>
       <c r="B21">
-        <v>1.2711500061259091</v>
+        <v>1.1512287994375818</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.629711395526185</v>
+        <v>3.55584009972315</v>
       </c>
       <c r="B22">
-        <v>0.755993885155263</v>
+        <v>0.63888262235460636</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.38822500295424</v>
+        <v>4.3163210471154994</v>
       </c>
       <c r="B23">
-        <v>0.22821846331211271</v>
+        <v>0.11424498947467202</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.1389584228353744</v>
+        <v>5.0692431515895064</v>
       </c>
       <c r="B24">
-        <v>-0.31233346573270993</v>
+        <v>-0.42283119327378721</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5.88181592519384</v>
+        <v>5.8145170248327878</v>
       </c>
       <c r="B25">
-        <v>-0.86581910830836428</v>
+        <v>-0.97249301996233062</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>6.6166606915546646</v>
+        <v>6.5520149291956562</v>
       </c>
       <c r="B26">
-        <v>-1.4324631456606867</v>
+        <v>-1.5349506909011013</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>7.3431915494459128</v>
+        <v>7.281455729679176</v>
       </c>
       <c r="B27">
-        <v>-2.0127601587022075</v>
+        <v>-2.1106668313545538</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>8.0610662378964122</v>
+        <v>8.0025199419471</v>
       </c>
       <c r="B28">
-        <v>-2.607272203262132</v>
+        <v>-2.700167172825723</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>8.769942495934993</v>
+        <v>8.7148880816631724</v>
       </c>
       <c r="B29">
-        <v>-3.21656133516966</v>
+        <v>-3.3039774468176386</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>9.4696598668465164</v>
+        <v>9.4184100345934336</v>
       </c>
       <c r="B30">
-        <v>-3.840891054033774</v>
+        <v>-3.9223446757126</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>10.160785110940017</v>
+        <v>10.113613166913067</v>
       </c>
       <c r="B31">
-        <v>-4.4793306345825821</v>
+        <v>-4.5544010454099748</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>10.844066792780573</v>
+        <v>10.801194214899548</v>
       </c>
       <c r="B32">
-        <v>-5.1306507953239828</v>
+        <v>-5.1990000326884056</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>11.520253476933258</v>
+        <v>11.481849914830342</v>
       </c>
       <c r="B33">
-        <v>-5.7936222547658591</v>
+        <v>-5.8549951143265258</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>12.189797943072689</v>
+        <v>12.156001285811112</v>
       </c>
       <c r="B34">
-        <v>-6.467501464923191</v>
+        <v>-6.5216934769932449</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>12.851969831311697</v>
+        <v>12.822966478260307</v>
       </c>
       <c r="B35">
-        <v>-7.1534878118393044</v>
+        <v>-7.20021714691859</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>13.505742996872669</v>
+        <v>13.481787925424566</v>
       </c>
       <c r="B36">
-        <v>-7.8532664150646161</v>
+        <v>-7.8921418602228552</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>14.150091294977978</v>
+        <v>14.131508060550528</v>
       </c>
       <c r="B37">
-        <v>-8.56852239414954</v>
+        <v>-8.59904335302634</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>14.783264410776559</v>
+        <v>14.770494375914215</v>
       </c>
       <c r="B38">
-        <v>-9.302130089868653</v>
+        <v>-9.3236080191270112</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>15.400615349123502</v>
+        <v>15.394414599909103</v>
       </c>
       <c r="B39">
-        <v>-10.061720727893148</v>
+        <v>-10.072964883033459</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>15.996772944800467</v>
+        <v>15.998261519958058</v>
       </c>
       <c r="B40">
-        <v>-10.856114755118394</v>
+        <v>-10.855353626931951</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>16.566366032589109</v>
+        <v>16.577027923483936</v>
       </c>
       <c r="B41">
-        <v>-11.694132618439751</v>
+        <v>-11.679013933008745</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>16.566366032589109</v>
+        <v>16.577027923483936</v>
       </c>
       <c r="B42">
-        <v>-11.694132618439751</v>
+        <v>-11.679013933008745</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>15.744123939261414</v>
+        <v>15.762809163129846</v>
       </c>
       <c r="B43">
-        <v>-11.271011159516819</v>
+        <v>-11.2428052400566</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>14.938707806603029</v>
+        <v>14.963946966398618</v>
       </c>
       <c r="B44">
-        <v>-10.820258360556164</v>
+        <v>-10.781326358995566</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>14.144795674763149</v>
+        <v>14.175483252340841</v>
       </c>
       <c r="B45">
-        <v>-10.350613864137161</v>
+        <v>-10.302736122838528</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>13.35706558389098</v>
+        <v>13.3924599400071</v>
       </c>
       <c r="B46">
-        <v>-9.8708173128391845</v>
+        <v>-9.8151933645983735</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>12.570917887333927</v>
+        <v>12.610592035326093</v>
       </c>
       <c r="B47">
-        <v>-9.3884221773501562</v>
+        <v>-9.3257493106358265</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>11.784642191232114</v>
+        <v>11.828286891738886</v>
       </c>
       <c r="B48">
-        <v>-8.90623724079214</v>
+        <v>-8.8370247607029242</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>10.997250414923856</v>
+        <v>11.044624949564655</v>
       </c>
       <c r="B49">
-        <v>-8.4258851143957436</v>
+        <v>-8.3505329078995381</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>10.207754477747461</v>
+        <v>10.258686649122577</v>
       </c>
       <c r="B50">
-        <v>-7.9489884093915766</v>
+        <v>-7.8677869453255331</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>9.4154601313010211</v>
+        <v>9.46982619819919</v>
       </c>
       <c r="B51">
-        <v>-7.4766872100839326</v>
+        <v>-7.3898495645513673</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>8.62084845622174</v>
+        <v>8.678492874450539</v>
       </c>
       <c r="B52">
-        <v>-7.0081914930718687</v>
+        <v>-6.9159814510298592</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>7.8246943654066046</v>
+        <v>7.8854097230000324</v>
       </c>
       <c r="B53">
-        <v>-6.5422287080281372</v>
+        <v>-6.4449927886844121</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>7.0277727717525842</v>
+        <v>7.0912997889710772</v>
       </c>
       <c r="B54">
-        <v>-6.0775263046254793</v>
+        <v>-5.9756937614384249</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>6.23067499383846</v>
+        <v>6.2967149600052474</v>
       </c>
       <c r="B55">
-        <v>-5.6131132283700689</v>
+        <v>-5.5071762035811274</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5.4332579729702157</v>
+        <v>5.5015224938167835</v>
       </c>
       <c r="B56">
-        <v>-5.1492244081017793</v>
+        <v>-5.0396585508650418</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4.6351950561356379</v>
+        <v>4.7054184906380989</v>
       </c>
       <c r="B57">
-        <v>-4.6863962684939056</v>
+        <v>-4.5736408894085194</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3.8361595903225054</v>
+        <v>3.9080990507015976</v>
       </c>
       <c r="B58">
-        <v>-4.2251652342197445</v>
+        <v>-4.1096233053299054</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.035864282164396</v>
+        <v>3.1092968973144375</v>
       </c>
       <c r="B59">
-        <v>-3.7660030941330924</v>
+        <v>-3.6480456191822279</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.2341792768780637</v>
+        <v>2.3088912460827773</v>
       </c>
       <c r="B60">
-        <v>-3.30912309380975</v>
+        <v>-3.1891065892572392</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.431014079326064</v>
+        <v>1.5067979356875385</v>
       </c>
       <c r="B61">
-        <v>-2.8546738430060219</v>
+        <v>-2.7329447082813783</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.62627819437094245</v>
+        <v>0.70293280480962728</v>
       </c>
       <c r="B62">
-        <v>-2.4028039514782082</v>
+        <v>-2.279698468981076</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.17987489265259529</v>
+        <v>-0.1025609932500134</v>
       </c>
       <c r="B63">
-        <v>-1.9532613679136253</v>
+        <v>-1.8291323036256961</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.98631577452125874</v>
+        <v>-0.90863104671036432</v>
       </c>
       <c r="B64">
-        <v>-1.504191396723632</v>
+        <v>-1.3795144026562973</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.7916710635395972</v>
+        <v>-1.7139976291703716</v>
       </c>
       <c r="B65">
-        <v>-1.0533386812506049</v>
+        <v>-0.928738896056869</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.5945673720121678</v>
+        <v>-2.51738101422899</v>
       </c>
       <c r="B66">
-        <v>-0.59844786483691559</v>
+        <v>-0.474699913811396</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.3954094461761528</v>
+        <v>-3.3191586279863095</v>
       </c>
       <c r="B67">
-        <v>-0.14018361567763746</v>
+        <v>-0.018018534227539448</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.2017145679992165</v>
+        <v>-4.1263365065469522</v>
       </c>
       <c r="B68">
-        <v>0.30910929862134368</v>
+        <v>0.429776371092325</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.0193072656563844</v>
+        <v>-4.9443432197284478</v>
       </c>
       <c r="B69">
-        <v>0.7398659253226374</v>
+        <v>0.85975175020898409</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-5.8401285164215357</v>
+        <v>-5.76566886219533</v>
       </c>
       <c r="B70">
-        <v>1.1653206705735968</v>
+        <v>1.2842656231305294</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-6.6553917498434734</v>
+        <v>-6.5821255553610305</v>
       </c>
       <c r="B71">
-        <v>1.5999027084745447</v>
+        <v>1.7167916573503439</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-7.4672837554717875</v>
+        <v>-7.395752002787491</v>
       </c>
       <c r="B72">
-        <v>2.0400209260529012</v>
+        <v>2.1539750383556413</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-8.2794519935125148</v>
+        <v>-8.2099482198315581</v>
       </c>
       <c r="B73">
-        <v>2.4796855189100984</v>
+        <v>2.5902208277376286</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-9.0904132467967056</v>
+        <v>-9.0233328868811871</v>
       </c>
       <c r="B74">
-        <v>2.9213322040165117</v>
+        <v>3.0278020735096502</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-9.8973739752530161</v>
+        <v>-9.8333036107535428</v>
       </c>
       <c r="B75">
-        <v>3.3695484909436453</v>
+        <v>3.4710011767920763</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-10.697430024575558</v>
+        <v>-10.637155038951494</v>
       </c>
       <c r="B76">
-        <v>3.8291035382985723</v>
+        <v>3.9242699647112458</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-11.487894410859056</v>
+        <v>-11.432384272986306</v>
       </c>
       <c r="B77">
-        <v>4.3044098707163814</v>
+        <v>4.3917271136312648</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-12.267059446035303</v>
+        <v>-12.21740118971724</v>
       </c>
       <c r="B78">
-        <v>4.798271827908696</v>
+        <v>4.8759892708613775</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-13.032003546906616</v>
+        <v>-12.989484457212258</v>
       </c>
       <c r="B79">
-        <v>5.31548718994705</v>
+        <v>5.3815345586897525</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-13.777590008952981</v>
+        <v>-13.743848520851781</v>
       </c>
       <c r="B80">
-        <v>5.8644913758874768</v>
+        <v>5.91623790723826</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-14.491178662020328</v>
+        <v>-14.468715185538004</v>
       </c>
       <c r="B81">
-        <v>6.4660418834162172</v>
+        <v>6.4994810748881715</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-14.944835058430154</v>
+        <v>-14.951666171112036</v>
       </c>
       <c r="B82">
-        <v>7.4944492410017158</v>
+        <v>7.4808116576517367</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-18.243394216921391</v>
+        <v>-18.183801229504873</v>
       </c>
       <c r="B1">
-        <v>6.3672881737029945</v>
+        <v>6.5355308955612763</v>
       </c>
       <c r="C1">
         <v>221.20000756679073</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-17.067290406473358</v>
+        <v>-17.048161783802186</v>
       </c>
       <c r="B2">
-        <v>6.4355157176234634</v>
+        <v>6.4917650960808588</v>
       </c>
       <c r="C2">
         <v>221.20000756679073</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-15.983425694058186</v>
+        <v>-15.981399575214214</v>
       </c>
       <c r="B3">
-        <v>6.2703163910635569</v>
+        <v>6.2782969741932577</v>
       </c>
       <c r="C3">
         <v>221.20000756679073</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-14.914031357004014</v>
+        <v>-14.925895595076032</v>
       </c>
       <c r="B4">
-        <v>6.0684972958021746</v>
+        <v>6.0370904064249391</v>
       </c>
       <c r="C4">
         <v>221.20000756679073</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-13.854784741296022</v>
+        <v>-13.878446567309256</v>
       </c>
       <c r="B5">
-        <v>5.8409976498105527</v>
+        <v>5.7760377446265938</v>
       </c>
       <c r="C5">
         <v>221.20000756679073</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-12.803923556933665</v>
+        <v>-12.837746208396347</v>
       </c>
       <c r="B6">
-        <v>5.5922772304334041</v>
+        <v>5.4983574591657192</v>
       </c>
       <c r="C6">
         <v>221.20000756679073</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-11.760441988827795</v>
+        <v>-11.803048748828079</v>
       </c>
       <c r="B7">
-        <v>5.3248814254027144</v>
+        <v>5.2058870049548158</v>
       </c>
       <c r="C7">
         <v>221.20000756679073</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-10.723748731237802</v>
+        <v>-10.773915549829093</v>
       </c>
       <c r="B8">
-        <v>5.0403066353931729</v>
+        <v>4.8997071166748176</v>
       </c>
       <c r="C8">
         <v>221.20000756679073</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-9.6929192813463168</v>
+        <v>-9.7496611612117974</v>
       </c>
       <c r="B9">
-        <v>4.7408924734756974</v>
+        <v>4.5815066322292335</v>
       </c>
       <c r="C9">
         <v>221.20000756679073</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-8.6669554761510916</v>
+        <v>-8.7295455839046117</v>
       </c>
       <c r="B10">
-        <v>4.4291649624628846</v>
+        <v>4.2531087891096773</v>
       </c>
       <c r="C10">
         <v>221.20000756679073</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-7.6448977089870844</v>
+        <v>-7.7128574347122045</v>
       </c>
       <c r="B11">
-        <v>4.10755255173781</v>
+        <v>3.91626631993765</v>
       </c>
       <c r="C11">
         <v>221.20000756679073</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-6.6262337795604882</v>
+        <v>-6.699216835411657</v>
       </c>
       <c r="B12">
-        <v>3.7773514520635034</v>
+        <v>3.5719151829391356</v>
       </c>
       <c r="C12">
         <v>221.20000756679073</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-5.6122025567252249</v>
+        <v>-5.6895413117934774</v>
       </c>
       <c r="B13">
-        <v>3.4354264931523688</v>
+        <v>3.2177947436281977</v>
       </c>
       <c r="C13">
         <v>221.20000756679073</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-4.6035450256461843</v>
+        <v>-4.6843795363780867</v>
       </c>
       <c r="B14">
-        <v>3.0799024848540215</v>
+        <v>2.8525531620522386</v>
       </c>
       <c r="C14">
         <v>221.20000756679073</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.5972595675843575</v>
+        <v>-3.6815073645921217</v>
       </c>
       <c r="B15">
-        <v>2.7183755386175541</v>
+        <v>2.4816703691039579</v>
       </c>
       <c r="C15">
         <v>221.20000756679073</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.5905931126220203</v>
+        <v>-2.6788848221755415</v>
       </c>
       <c r="B16">
-        <v>2.3578127704362237</v>
+        <v>2.1101725299444771</v>
       </c>
       <c r="C16">
         <v>221.20000756679073</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.5855293900304686</v>
+        <v>-1.6779814332153491</v>
       </c>
       <c r="B17">
-        <v>1.9931940128804435</v>
+        <v>1.7344389759633081</v>
       </c>
       <c r="C17">
         <v>221.20000756679073</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.58463005442361893</v>
+        <v>-0.68069493200685915</v>
       </c>
       <c r="B18">
-        <v>1.6180365592398183</v>
+        <v>1.3497939981640243</v>
       </c>
       <c r="C18">
         <v>221.20000756679073</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.41196833740314648</v>
+        <v>0.31287360466844355</v>
       </c>
       <c r="B19">
-        <v>1.2319948291035643</v>
+        <v>0.95598855977805108</v>
       </c>
       <c r="C19">
         <v>221.20000756679073</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.4047355031090816</v>
+        <v>1.3030722644075305</v>
       </c>
       <c r="B20">
-        <v>0.83625752363580008</v>
+        <v>0.55388029209377476</v>
       </c>
       <c r="C20">
         <v>221.20000756679073</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.3941411603534366</v>
+        <v>2.2902491348073704</v>
       </c>
       <c r="B21">
-        <v>0.43201334400064512</v>
+        <v>0.14432682639958402</v>
       </c>
       <c r="C21">
         <v>221.20000756679073</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.380571402739466</v>
+        <v>3.2746903217932553</v>
       </c>
       <c r="B22">
-        <v>0.02023936633436434</v>
+        <v>-0.27196691878558638</v>
       </c>
       <c r="C22">
         <v>221.20000756679073</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.3640778276463976</v>
+        <v>4.2564340046037232</v>
       </c>
       <c r="B23">
-        <v>-0.39893383333817078</v>
+        <v>-0.69490687602059176</v>
       </c>
       <c r="C23">
         <v>221.20000756679073</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.3446284083974556</v>
+        <v>5.2354563808056325</v>
       </c>
       <c r="B24">
-        <v>-0.82558730401994029</v>
+        <v>-1.1245516906337389</v>
       </c>
       <c r="C24">
         <v>221.20000756679073</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>6.3221911183158666</v>
+        <v>6.211733647965838</v>
       </c>
       <c r="B25">
-        <v>-1.259802094713925</v>
+        <v>-1.5609600079533339</v>
       </c>
       <c r="C25">
         <v>221.20000756679073</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>7.2967201228103811</v>
+        <v>7.1852317492010185</v>
       </c>
       <c r="B26">
-        <v>-1.70169419772081</v>
+        <v>-2.0042157386069674</v>
       </c>
       <c r="C26">
         <v>221.20000756679073</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>8.26811435563188</v>
+        <v>8.1558756098271612</v>
       </c>
       <c r="B27">
-        <v>-2.1515193785321087</v>
+        <v>-2.45450385441938</v>
       </c>
       <c r="C27">
         <v>221.20000756679073</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>9.2362589426167609</v>
+        <v>9.12357990071007</v>
       </c>
       <c r="B28">
-        <v>-2.6095683459370376</v>
+        <v>-2.9120345925145945</v>
       </c>
       <c r="C28">
         <v>221.20000756679073</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>10.201039009601429</v>
+        <v>10.088259292715549</v>
       </c>
       <c r="B29">
-        <v>-3.0761318087248148</v>
+        <v>-3.3770181900166341</v>
       </c>
       <c r="C29">
         <v>221.20000756679073</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>11.162401921526318</v>
+        <v>11.049874544712351</v>
       </c>
       <c r="B30">
-        <v>-3.5513429689485094</v>
+        <v>-3.8495513306977478</v>
       </c>
       <c r="C30">
         <v>221.20000756679073</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>12.120543999748007</v>
+        <v>12.008570767581023</v>
       </c>
       <c r="B31">
-        <v>-4.0347050017165946</v>
+        <v>-4.3292764849230894</v>
       </c>
       <c r="C31">
         <v>221.20000756679073</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>13.075723804727113</v>
+        <v>12.964539160205058</v>
       </c>
       <c r="B32">
-        <v>-4.5255635754014012</v>
+        <v>-4.8157225697060442</v>
       </c>
       <c r="C32">
         <v>221.20000756679073</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>14.028199896924241</v>
+        <v>13.917970921467939</v>
       </c>
       <c r="B33">
-        <v>-5.0232643583752505</v>
+        <v>-5.3084185020599852</v>
       </c>
       <c r="C33">
         <v>221.20000756679073</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>14.978130175341633</v>
+        <v>14.86898264527021</v>
       </c>
       <c r="B34">
-        <v>-5.5274077601095346</v>
+        <v>-5.8070770135559293</v>
       </c>
       <c r="C34">
         <v>221.20000756679073</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>15.925269893147954</v>
+        <v>15.817392505580566</v>
       </c>
       <c r="B35">
-        <v>-6.0386131544718742</v>
+        <v>-6.3121460939954028</v>
       </c>
       <c r="C35">
         <v>221.20000756679073</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>16.869273642053496</v>
+        <v>16.762944071384755</v>
       </c>
       <c r="B36">
-        <v>-6.5577546564289593</v>
+        <v>-6.8242575477375649</v>
       </c>
       <c r="C36">
         <v>221.20000756679073</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>17.809796013768572</v>
+        <v>17.705380911668534</v>
       </c>
       <c r="B37">
-        <v>-7.085706380947479</v>
+        <v>-7.3440431791415817</v>
       </c>
       <c r="C37">
         <v>221.20000756679073</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>18.74624479188617</v>
+        <v>18.644263713846911</v>
       </c>
       <c r="B38">
-        <v>-7.6239670332996985</v>
+        <v>-7.8725853830458066</v>
       </c>
       <c r="C38">
         <v>221.20000756679073</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>19.677040527530167</v>
+        <v>19.578421639052017</v>
       </c>
       <c r="B39">
-        <v>-8.1765336799802366</v>
+        <v>-8.4127689162054136</v>
       </c>
       <c r="C39">
         <v>221.20000756679073</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>20.600356963707124</v>
+        <v>20.506500966845241</v>
       </c>
       <c r="B40">
-        <v>-8.74802797778928</v>
+        <v>-8.9679291258547558</v>
       </c>
       <c r="C40">
         <v>221.20000756679073</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>21.514367843423631</v>
+        <v>21.427147976787975</v>
       </c>
       <c r="B41">
-        <v>-9.3430715835270277</v>
+        <v>-9.5414013592282085</v>
       </c>
       <c r="C41">
         <v>221.20000756679073</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>21.514367843423631</v>
+        <v>21.427147976787975</v>
       </c>
       <c r="B42">
-        <v>-9.3430715835270277</v>
+        <v>-9.5414013592282085</v>
       </c>
       <c r="C42">
         <v>221.20000756679073</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>20.514168408137987</v>
+        <v>20.442644450796266</v>
       </c>
       <c r="B43">
-        <v>-8.9661429119852016</v>
+        <v>-9.1252612072257726</v>
       </c>
       <c r="C43">
         <v>221.20000756679073</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>19.519465619165146</v>
+        <v>19.461675458558769</v>
       </c>
       <c r="B44">
-        <v>-8.5753040334454944</v>
+        <v>-8.7004125382757316</v>
       </c>
       <c r="C44">
         <v>221.20000756679073</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>18.528437886152908</v>
+        <v>18.482892055165635</v>
       </c>
       <c r="B45">
-        <v>-8.175164794971451</v>
+        <v>-8.270178933485429</v>
       </c>
       <c r="C45">
         <v>221.20000756679073</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>17.539263618749072</v>
+        <v>17.504945295707042</v>
       </c>
       <c r="B46">
-        <v>-7.7703350436266208</v>
+        <v>-7.8378839739622119</v>
       </c>
       <c r="C46">
         <v>221.20000756679073</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>16.550367871065021</v>
+        <v>16.526668949371576</v>
       </c>
       <c r="B47">
-        <v>-7.3648004503227451</v>
+        <v>-7.4064010629586621</v>
       </c>
       <c r="C47">
         <v>221.20000756679073</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>15.561162275066494</v>
+        <v>15.547627641741734</v>
       </c>
       <c r="B48">
-        <v>-6.9600499813643717</v>
+        <v>-6.9768028923083465</v>
       </c>
       <c r="C48">
         <v>221.20000756679073</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>14.571305107182781</v>
+        <v>14.567568712498435</v>
       </c>
       <c r="B49">
-        <v>-6.5569484269042393</v>
+        <v>-6.5497119759900686</v>
       </c>
       <c r="C49">
         <v>221.20000756679073</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>13.580454643843186</v>
+        <v>13.586239501322613</v>
       </c>
       <c r="B50">
-        <v>-6.156360577095084</v>
+        <v>-6.1257508279826318</v>
       </c>
       <c r="C50">
         <v>221.20000756679073</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>12.588369641718797</v>
+        <v>12.603461767433197</v>
       </c>
       <c r="B51">
-        <v>-5.7588969395903495</v>
+        <v>-5.70535860461351</v>
       </c>
       <c r="C51">
         <v>221.20000756679073</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>11.595210778447756</v>
+        <v>11.619354948201018</v>
       </c>
       <c r="B52">
-        <v>-5.3641508920462533</v>
+        <v>-5.2882410316048167</v>
       </c>
       <c r="C52">
         <v>221.20000756679073</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>10.601239211909991</v>
+        <v>10.634112900534912</v>
       </c>
       <c r="B53">
-        <v>-4.9714615296197211</v>
+        <v>-4.8739204770273385</v>
       </c>
       <c r="C53">
         <v>221.20000756679073</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>9.6067160999854178</v>
+        <v>9.6479294813436987</v>
       </c>
       <c r="B54">
-        <v>-4.5801679474676664</v>
+        <v>-4.4619193089518525</v>
       </c>
       <c r="C54">
         <v>221.20000756679073</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>8.6118401877708681</v>
+        <v>8.66095228180172</v>
       </c>
       <c r="B55">
-        <v>-4.1897671870078224</v>
+        <v>-4.0518738867025492</v>
       </c>
       <c r="C55">
         <v>221.20000756679073</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>7.6165605692308134</v>
+        <v>7.6731438301453725</v>
       </c>
       <c r="B56">
-        <v>-3.8003880747011527</v>
+        <v>-3.6438765346172572</v>
       </c>
       <c r="C56">
         <v>221.20000756679073</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>6.6207639255466324</v>
+        <v>6.6844203888765694</v>
       </c>
       <c r="B57">
-        <v>-3.4123173832694369</v>
+        <v>-3.2381335682872106</v>
       </c>
       <c r="C57">
         <v>221.20000756679073</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5.6243369378997086</v>
+        <v>5.6946982204972283</v>
       </c>
       <c r="B58">
-        <v>-3.0258418854344504</v>
+        <v>-2.8348513033036484</v>
       </c>
       <c r="C58">
         <v>221.20000756679073</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.6271799235969624</v>
+        <v>4.7039036661621232</v>
       </c>
       <c r="B59">
-        <v>-2.641213845361619</v>
+        <v>-2.4342112230945103</v>
       </c>
       <c r="C59">
         <v>221.20000756679073</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.6292477444475182</v>
+        <v>3.712003381637536</v>
       </c>
       <c r="B60">
-        <v>-2.258547492990969</v>
+        <v>-2.0362954824345709</v>
       </c>
       <c r="C60">
         <v>221.20000756679073</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.6305088983860418</v>
+        <v>2.7189741013426114</v>
       </c>
       <c r="B61">
-        <v>-1.8779225497061758</v>
+        <v>-1.6411614039353115</v>
       </c>
       <c r="C61">
         <v>221.20000756679073</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.630931883347202</v>
+        <v>1.7247925596964948</v>
       </c>
       <c r="B62">
-        <v>-1.4994187368909164</v>
+        <v>-1.2488663102082116</v>
       </c>
       <c r="C62">
         <v>221.20000756679073</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.63056864304686422</v>
+        <v>0.72949729035549737</v>
       </c>
       <c r="B63">
-        <v>-1.1229046020560243</v>
+        <v>-0.85931526058433882</v>
       </c>
       <c r="C63">
         <v>221.20000756679073</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.37019509567433639</v>
+        <v>-0.26662597607544336</v>
       </c>
       <c r="B64">
-        <v>-0.747403997220961</v>
+        <v>-0.47180426127309877</v>
       </c>
       <c r="C64">
         <v>221.20000756679073</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.3708901601945598</v>
+        <v>-1.26322970975422</v>
       </c>
       <c r="B65">
-        <v>-0.37172960053234844</v>
+        <v>-0.085477055203485808</v>
       </c>
       <c r="C65">
         <v>221.20000756679073</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.3710473778919696</v>
+        <v>-2.2599663808387285</v>
       </c>
       <c r="B66">
-        <v>0.0053059098631919955</v>
+        <v>0.30052261469550651</v>
       </c>
       <c r="C66">
         <v>221.20000756679073</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.3708039940035079</v>
+        <v>-3.25693777061554</v>
       </c>
       <c r="B67">
-        <v>0.3833552113353334</v>
+        <v>0.68594397586922573</v>
       </c>
       <c r="C67">
         <v>221.20000756679073</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.3727229252012316</v>
+        <v>-4.2560429048859225</v>
       </c>
       <c r="B68">
-        <v>0.75593240331892342</v>
+        <v>1.0661081372603845</v>
       </c>
       <c r="C68">
         <v>221.20000756679073</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.3787893698891489</v>
+        <v>-5.2587528111491206</v>
       </c>
       <c r="B69">
-        <v>1.1180136004918735</v>
+        <v>1.4373907260949954</v>
       </c>
       <c r="C69">
         <v>221.20000756679073</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-6.3862519819639472</v>
+        <v>-6.2630292791815565</v>
       </c>
       <c r="B70">
-        <v>1.4765615564391694</v>
+        <v>1.8048135612349061</v>
       </c>
       <c r="C70">
         <v>221.20000756679073</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-7.3921110235466942</v>
+        <v>-7.26665008915637</v>
       </c>
       <c r="B71">
-        <v>1.8391676227706506</v>
+        <v>2.1738518313101425</v>
       </c>
       <c r="C71">
         <v>221.20000756679073</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-8.3971097341632586</v>
+        <v>-8.2701662205563533</v>
       </c>
       <c r="B72">
-        <v>2.2039509042884906</v>
+        <v>2.5431480123876038</v>
       </c>
       <c r="C72">
         <v>221.20000756679073</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-9.4024894167274837</v>
+        <v>-9.2744976900262674</v>
       </c>
       <c r="B73">
-        <v>2.5677700708986593</v>
+        <v>2.9104353329211397</v>
       </c>
       <c r="C73">
         <v>221.20000756679073</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-10.407740650300283</v>
+        <v>-10.279267463549072</v>
       </c>
       <c r="B74">
-        <v>2.9319142997299985</v>
+        <v>3.2766427434755343</v>
       </c>
       <c r="C74">
         <v>221.20000756679073</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-11.411906781962614</v>
+        <v>-11.283767180595694</v>
       </c>
       <c r="B75">
-        <v>3.2988045652043061</v>
+        <v>3.64351552931368</v>
       </c>
       <c r="C75">
         <v>221.20000756679073</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-12.413992954728563</v>
+        <v>-12.28726022525073</v>
       </c>
       <c r="B76">
-        <v>3.6709585236923612</v>
+        <v>4.0128685923800047</v>
       </c>
       <c r="C76">
         <v>221.20000756679073</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-13.4130781519927</v>
+        <v>-13.289064714882898</v>
       </c>
       <c r="B77">
-        <v>4.0507069658073869</v>
+        <v>4.3863819806988626</v>
       </c>
       <c r="C77">
         <v>221.20000756679073</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-14.408574922738382</v>
+        <v>-14.288745955383737</v>
       </c>
       <c r="B78">
-        <v>4.43953653718339</v>
+        <v>4.7651267099327939</v>
       </c>
       <c r="C78">
         <v>221.20000756679073</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-15.399481473502421</v>
+        <v>-15.285562292707281</v>
       </c>
       <c r="B79">
-        <v>4.8399824481375129</v>
+        <v>5.1509300951614376</v>
       </c>
       <c r="C79">
         <v>221.20000756679073</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-16.384039867867553</v>
+        <v>-16.278211898502136</v>
       </c>
       <c r="B80">
-        <v>5.2564934585247594</v>
+        <v>5.5469996299466784</v>
       </c>
       <c r="C80">
         <v>221.20000756679073</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-17.357932061982112</v>
+        <v>-17.263496214422837</v>
       </c>
       <c r="B81">
-        <v>5.69999711950708</v>
+        <v>5.9612160424117722</v>
       </c>
       <c r="C81">
         <v>221.20000756679073</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-18.243394216921391</v>
+        <v>-18.183801229504873</v>
       </c>
       <c r="B82">
-        <v>6.3672881737029945</v>
+        <v>6.5355308955612763</v>
       </c>
       <c r="C82">
         <v>221.20000756679073</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-20.858612944174688</v>
+        <v>-20.775317333651994</v>
       </c>
       <c r="B1">
-        <v>5.8660830553534211</v>
+        <v>6.1545799250034525</v>
       </c>
       <c r="C1">
         <v>245.30998079303629</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-19.613963401739003</v>
+        <v>-19.558562096193537</v>
       </c>
       <c r="B2">
-        <v>5.8332646598278233</v>
+        <v>6.020097120257546</v>
       </c>
       <c r="C2">
         <v>245.30998079303629</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-18.419124822520303</v>
+        <v>-18.376868761053849</v>
       </c>
       <c r="B3">
-        <v>5.6389219748519217</v>
+        <v>5.7772725690766746</v>
       </c>
       <c r="C3">
         <v>245.30998079303629</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-17.232119398958268</v>
+        <v>-17.200997027874237</v>
       </c>
       <c r="B4">
-        <v>5.4191783576337516</v>
+        <v>5.5164591900886295</v>
       </c>
       <c r="C4">
         <v>245.30998079303629</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-16.050614576599024</v>
+        <v>-16.029321961129934</v>
       </c>
       <c r="B5">
-        <v>5.1815976892234961</v>
+        <v>5.2426780557668318</v>
       </c>
       <c r="C5">
         <v>245.30998079303629</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-14.873659811564762</v>
+        <v>-14.861181289756434</v>
       </c>
       <c r="B6">
-        <v>4.9292623417443995</v>
+        <v>4.9579755925455489</v>
       </c>
       <c r="C6">
         <v>245.30998079303629</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-13.700712840574182</v>
+        <v>-13.696197147121577</v>
       </c>
       <c r="B7">
-        <v>4.6639307371491983</v>
+        <v>4.6635194133647682</v>
       </c>
       <c r="C7">
         <v>245.30998079303629</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-12.531455119677817</v>
+        <v>-12.534147506863103</v>
       </c>
       <c r="B8">
-        <v>4.38663583247733</v>
+        <v>4.3599955826491659</v>
       </c>
       <c r="C8">
         <v>245.30998079303629</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-11.365388187886827</v>
+        <v>-11.37468503263807</v>
       </c>
       <c r="B9">
-        <v>4.0989940099836586</v>
+        <v>4.0484773743372822</v>
       </c>
       <c r="C9">
         <v>245.30998079303629</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-10.20197379342188</v>
+        <v>-10.217434677892376</v>
       </c>
       <c r="B10">
-        <v>3.8027506833399216</v>
+        <v>3.7301236872902326</v>
       </c>
       <c r="C10">
         <v>245.30998079303629</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-9.0406944383810952</v>
+        <v>-9.0620358652079336</v>
       </c>
       <c r="B11">
-        <v>3.4995839666698991</v>
+        <v>3.4060487105456021</v>
       </c>
       <c r="C11">
         <v>245.30998079303629</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-7.8812741005504039</v>
+        <v>-7.9082962261649117</v>
       </c>
       <c r="B12">
-        <v>3.1903889298361316</v>
+        <v>3.0768468650898533</v>
       </c>
       <c r="C12">
         <v>245.30998079303629</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-6.72438190658956</v>
+        <v>-6.7566817592004709</v>
       </c>
       <c r="B13">
-        <v>2.8729957652041542</v>
+        <v>2.7410782095285091</v>
       </c>
       <c r="C13">
         <v>245.30998079303629</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-5.5704182019174366</v>
+        <v>-5.60747124666475</v>
       </c>
       <c r="B14">
-        <v>2.5461062543669706</v>
+        <v>2.3978813026763612</v>
       </c>
       <c r="C14">
         <v>245.30998079303629</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-4.4177630581155949</v>
+        <v>-4.4595362397028042</v>
       </c>
       <c r="B15">
-        <v>2.2149734133244623</v>
+        <v>2.0507430665662016</v>
       </c>
       <c r="C15">
         <v>245.30998079303629</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.2649306845426125</v>
+        <v>-3.3118417304170618</v>
       </c>
       <c r="B16">
-        <v>1.8844152833697234</v>
+        <v>1.7028616894246087</v>
       </c>
       <c r="C16">
         <v>245.30998079303629</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.1129921155024167</v>
+        <v>-2.1651337059444966</v>
       </c>
       <c r="B17">
-        <v>1.5509587725618186</v>
+        <v>1.3519320610352776</v>
       </c>
       <c r="C17">
         <v>245.30998079303629</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.96333030836960376</v>
+        <v>-1.0203754346203622</v>
       </c>
       <c r="B18">
-        <v>1.2101193017469762</v>
+        <v>0.994977669377315</v>
       </c>
       <c r="C18">
         <v>245.30998079303629</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.18398091214389761</v>
+        <v>0.12238168546150952</v>
       </c>
       <c r="B19">
-        <v>0.8616574761541087</v>
+        <v>0.63183969365435555</v>
       </c>
       <c r="C19">
         <v>245.30998079303629</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.3291950044918384</v>
+        <v>1.2633142237676549</v>
       </c>
       <c r="B20">
-        <v>0.50639519710779624</v>
+        <v>0.263063735876162</v>
       </c>
       <c r="C20">
         <v>245.30998079303629</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.4725654271279653</v>
+        <v>2.402598749764608</v>
       </c>
       <c r="B21">
-        <v>0.14515436593261927</v>
+        <v>-0.11080460194750122</v>
       </c>
       <c r="C21">
         <v>245.30998079303629</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.6143005285105554</v>
+        <v>3.5403804044672595</v>
       </c>
       <c r="B22">
-        <v>-0.22138939629310553</v>
+        <v>-0.4893168321421929</v>
       </c>
       <c r="C22">
         <v>245.30998079303629</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.75442821711598</v>
+        <v>4.6766786150839206</v>
       </c>
       <c r="B23">
-        <v>-0.59314558947611706</v>
+        <v>-0.87241292437475437</v>
       </c>
       <c r="C23">
         <v>245.30998079303629</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.8929312914251488</v>
+        <v>5.81148138037127</v>
       </c>
       <c r="B24">
-        <v>-0.97016999376942159</v>
+        <v>-1.2601299626473517</v>
       </c>
       <c r="C24">
         <v>245.30998079303629</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>7.0297925499189562</v>
+        <v>6.9447766990859749</v>
       </c>
       <c r="B25">
-        <v>-1.3525183893260222</v>
+        <v>-1.6525050309621474</v>
       </c>
       <c r="C25">
         <v>245.30998079303629</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>8.1649873659565255</v>
+        <v>8.07654739161277</v>
       </c>
       <c r="B26">
-        <v>-1.7402706340810581</v>
+        <v>-2.0495912145597437</v>
       </c>
       <c r="C26">
         <v>245.30998079303629</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>9.2984614124098446</v>
+        <v>9.2067555648486668</v>
       </c>
       <c r="B27">
-        <v>-2.1336028970982079</v>
+        <v>-2.4515056036344971</v>
       </c>
       <c r="C27">
         <v>245.30998079303629</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>10.43015293702911</v>
+        <v>10.335358147318722</v>
       </c>
       <c r="B28">
-        <v>-2.53271542522328</v>
+        <v>-2.8583812896191945</v>
       </c>
       <c r="C28">
         <v>245.30998079303629</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>11.560000187564524</v>
+        <v>11.462312067548005</v>
       </c>
       <c r="B29">
-        <v>-2.9378084653020879</v>
+        <v>-3.2703513639466308</v>
       </c>
       <c r="C29">
         <v>245.30998079303629</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>12.687975036304367</v>
+        <v>12.587597669261875</v>
       </c>
       <c r="B30">
-        <v>-3.3489732283523415</v>
+        <v>-3.687476564767965</v>
       </c>
       <c r="C30">
         <v>245.30998079303629</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>13.814183853689279</v>
+        <v>13.71128895698685</v>
       </c>
       <c r="B31">
-        <v>-3.7658647820793529</v>
+        <v>-4.1095282171078376</v>
       </c>
       <c r="C31">
         <v>245.30998079303629</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>14.938766634698002</v>
+        <v>14.833483350449782</v>
       </c>
       <c r="B32">
-        <v>-4.1880291583603437</v>
+        <v>-4.5362052927092655</v>
       </c>
       <c r="C32">
         <v>245.30998079303629</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>16.061863374309244</v>
+        <v>15.954278269377474</v>
       </c>
       <c r="B33">
-        <v>-4.6150123890725254</v>
+        <v>-4.96720676331526</v>
       </c>
       <c r="C33">
         <v>245.30998079303629</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>17.183559761702611</v>
+        <v>17.073733299597887</v>
       </c>
       <c r="B34">
-        <v>-5.0465366059926691</v>
+        <v>-5.4023485079216993</v>
       </c>
       <c r="C34">
         <v>245.30998079303629</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>18.303724262861124</v>
+        <v>18.191756691343379</v>
       </c>
       <c r="B35">
-        <v>-5.4830283404957587</v>
+        <v>-5.8419140345359075</v>
       </c>
       <c r="C35">
         <v>245.30998079303629</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>19.422171037968653</v>
+        <v>19.308218860947438</v>
       </c>
       <c r="B36">
-        <v>-5.9250902238563254</v>
+        <v>-6.2863037584180725</v>
       </c>
       <c r="C36">
         <v>245.30998079303629</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>20.538714247209114</v>
+        <v>20.42299022474355</v>
       </c>
       <c r="B37">
-        <v>-6.37332488734891</v>
+        <v>-6.7359180948283894</v>
       </c>
       <c r="C37">
         <v>245.30998079303629</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>21.653034854040072</v>
+        <v>21.53584841348777</v>
       </c>
       <c r="B38">
-        <v>-6.8287668853666235</v>
+        <v>-7.1914441677004737</v>
       </c>
       <c r="C38">
         <v>245.30998079303629</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>22.764281035013948</v>
+        <v>22.646199915626497</v>
       </c>
       <c r="B39">
-        <v>-7.2941784647769</v>
+        <v>-7.6547159356616774</v>
       </c>
       <c r="C39">
         <v>245.30998079303629</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>23.871467769956851</v>
+        <v>23.753358434028673</v>
       </c>
       <c r="B40">
-        <v>-7.7727537955657438</v>
+        <v>-8.1278540660127838</v>
       </c>
       <c r="C40">
         <v>245.30998079303629</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>24.973610038694879</v>
+        <v>24.856637671563245</v>
       </c>
       <c r="B41">
-        <v>-8.26768704771916</v>
+        <v>-8.6129792260545646</v>
       </c>
       <c r="C41">
         <v>245.30998079303629</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>24.973610038694879</v>
+        <v>24.856637671563245</v>
       </c>
       <c r="B42">
-        <v>-8.26768704771916</v>
+        <v>-8.6129792260545646</v>
       </c>
       <c r="C42">
         <v>245.30998079303629</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>23.824944230760263</v>
+        <v>23.720951929984722</v>
       </c>
       <c r="B43">
-        <v>-7.9236178047338894</v>
+        <v>-8.2279905963143314</v>
       </c>
       <c r="C43">
         <v>245.30998079303629</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>22.679224006533659</v>
+        <v>22.58695246831245</v>
       </c>
       <c r="B44">
-        <v>-7.5699967826878094</v>
+        <v>-7.8377913391426013</v>
       </c>
       <c r="C44">
         <v>245.30998079303629</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>21.535465322339988</v>
+        <v>21.453954009702535</v>
       </c>
       <c r="B45">
-        <v>-7.2100149850295923</v>
+        <v>-7.4444989691392891</v>
       </c>
       <c r="C45">
         <v>245.30998079303629</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>20.392684134504169</v>
+        <v>20.321271277311062</v>
       </c>
       <c r="B46">
-        <v>-6.8468634152079195</v>
+        <v>-7.0502310009043123</v>
       </c>
       <c r="C46">
         <v>245.30998079303629</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>19.250029562355916</v>
+        <v>19.188311744637925</v>
       </c>
       <c r="B47">
-        <v>-6.4833012629030131</v>
+        <v>-6.656818349236465</v>
       </c>
       <c r="C47">
         <v>245.30998079303629</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>18.107183377244329</v>
+        <v>18.054853886558291</v>
       </c>
       <c r="B48">
-        <v>-6.1203604627213259</v>
+        <v>-6.2649455297300989</v>
       </c>
       <c r="C48">
         <v>245.30998079303629</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>16.963960513523286</v>
+        <v>16.920768928291132</v>
       </c>
       <c r="B49">
-        <v>-5.7586411355008513</v>
+        <v>-5.8750104581784388</v>
       </c>
       <c r="C49">
         <v>245.30998079303629</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>15.820175905546703</v>
+        <v>15.785928095055413</v>
       </c>
       <c r="B50">
-        <v>-5.3987434020795941</v>
+        <v>-5.4874110503747131</v>
       </c>
       <c r="C50">
         <v>245.30998079303629</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>14.675698755724769</v>
+        <v>14.65024040653368</v>
       </c>
       <c r="B51">
-        <v>-5.0410914057865011</v>
+        <v>-5.1024284367149964</v>
       </c>
       <c r="C51">
         <v>245.30998079303629</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>13.530615338692774</v>
+        <v>13.513766060262681</v>
       </c>
       <c r="B52">
-        <v>-4.6854053799142967</v>
+        <v>-4.7198766060067161</v>
       </c>
       <c r="C52">
         <v>245.30998079303629</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>12.385066197142322</v>
+        <v>12.37660304824275</v>
       </c>
       <c r="B53">
-        <v>-4.3312295802466592</v>
+        <v>-4.3394527616601435</v>
       </c>
       <c r="C53">
         <v>245.30998079303629</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>11.239191873764984</v>
+        <v>11.238849362474197</v>
       </c>
       <c r="B54">
-        <v>-3.9781082625672606</v>
+        <v>-3.9608541070855479</v>
       </c>
       <c r="C54">
         <v>245.30998079303629</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>10.093099250210365</v>
+        <v>10.10057954161625</v>
       </c>
       <c r="B55">
-        <v>-3.6256948368607129</v>
+        <v>-3.5838503168304263</v>
       </c>
       <c r="C55">
         <v>245.30998079303629</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>8.9467605639601668</v>
+        <v>8.9617743109637455</v>
       </c>
       <c r="B56">
-        <v>-3.2740793299153705</v>
+        <v>-3.2085009499911807</v>
       </c>
       <c r="C56">
         <v>245.30998079303629</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>7.8001143914540947</v>
+        <v>7.8223909424704061</v>
       </c>
       <c r="B57">
-        <v>-2.923460922720523</v>
+        <v>-2.8349380368014323</v>
       </c>
       <c r="C57">
         <v>245.30998079303629</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>6.653099309131866</v>
+        <v>6.6823867080899761</v>
       </c>
       <c r="B58">
-        <v>-2.5740387962654614</v>
+        <v>-2.4632936074948115</v>
       </c>
       <c r="C58">
         <v>245.30998079303629</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5.5056612822720616</v>
+        <v>5.5417240202381937</v>
       </c>
       <c r="B59">
-        <v>-2.2259881714135874</v>
+        <v>-2.0936838082086378</v>
       </c>
       <c r="C59">
         <v>245.30998079303629</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4.3577758315087713</v>
+        <v>4.4003858531789035</v>
       </c>
       <c r="B60">
-        <v>-1.879388428524752</v>
+        <v>-1.7261612486950362</v>
       </c>
       <c r="C60">
         <v>245.30998079303629</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3.2094258663149651</v>
+        <v>3.2583603216379693</v>
       </c>
       <c r="B61">
-        <v>-1.5342949878329228</v>
+        <v>-1.3607626546098308</v>
       </c>
       <c r="C61">
         <v>245.30998079303629</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2.0605942961636061</v>
+        <v>2.1156355403412483</v>
       </c>
       <c r="B62">
-        <v>-1.1907632695720627</v>
+        <v>-0.99752475160884335</v>
       </c>
       <c r="C62">
         <v>245.30998079303629</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.9113091028083431</v>
+        <v>0.9722310130602414</v>
       </c>
       <c r="B63">
-        <v>-0.84870253602936718</v>
+        <v>-0.63638727277767182</v>
       </c>
       <c r="C63">
         <v>245.30998079303629</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.23822144287446853</v>
+        <v>-0.17170820025102215</v>
       </c>
       <c r="B64">
-        <v>-0.50743741770494466</v>
+        <v>-0.276901980921004</v>
       </c>
       <c r="C64">
         <v>245.30998079303629</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.3877439977277919</v>
+        <v>-1.3160056505928759</v>
       </c>
       <c r="B65">
-        <v>-0.16614638715213267</v>
+        <v>0.081476353726697981</v>
       </c>
       <c r="C65">
         <v>245.30998079303629</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.5370052185945946</v>
+        <v>-2.4604848889656568</v>
       </c>
       <c r="B66">
-        <v>0.17599208307573189</v>
+        <v>0.43929296093097303</v>
       </c>
       <c r="C66">
         <v>245.30998079303629</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.6860790757862967</v>
+        <v>-3.6051974655916887</v>
       </c>
       <c r="B67">
-        <v>0.51873812606537606</v>
+        <v>0.79638854981633733</v>
       </c>
       <c r="C67">
         <v>245.30998079303629</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.8363487934881926</v>
+        <v>-4.7511069275812936</v>
       </c>
       <c r="B68">
-        <v>0.85760629746379724</v>
+        <v>1.149785746943232</v>
       </c>
       <c r="C68">
         <v>245.30998079303629</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.9888857165214135</v>
+        <v>-5.89895958651292</v>
       </c>
       <c r="B69">
-        <v>1.1891224984017264</v>
+        <v>1.4971784395668824</v>
       </c>
       <c r="C69">
         <v>245.30998079303629</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-7.1422044183765925</v>
+        <v>-7.0477208149495221</v>
       </c>
       <c r="B70">
-        <v>1.518103589384564</v>
+        <v>1.8417636402857274</v>
       </c>
       <c r="C70">
         <v>245.30998079303629</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-8.2946853678014012</v>
+        <v>-8.1962625790120676</v>
       </c>
       <c r="B71">
-        <v>1.8498012985034773</v>
+        <v>2.18702698885148</v>
       </c>
       <c r="C71">
         <v>245.30998079303629</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-9.446729385902163</v>
+        <v>-9.3448641580689973</v>
       </c>
       <c r="B72">
-        <v>2.1829158648180225</v>
+        <v>2.53210550828572</v>
       </c>
       <c r="C72">
         <v>245.30998079303629</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-10.599006112723016</v>
+        <v>-10.493992086963134</v>
       </c>
       <c r="B73">
-        <v>2.5152758159186912</v>
+        <v>2.875557599693308</v>
       </c>
       <c r="C73">
         <v>245.30998079303629</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-11.751240111700707</v>
+        <v>-11.643454609187327</v>
       </c>
       <c r="B74">
-        <v>2.8477743225513197</v>
+        <v>3.2179757932423652</v>
       </c>
       <c r="C74">
         <v>245.30998079303629</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-12.902914507005226</v>
+        <v>-12.792891797290411</v>
       </c>
       <c r="B75">
-        <v>3.1820874816187841</v>
+        <v>3.5604722695639941</v>
       </c>
       <c r="C75">
         <v>245.30998079303629</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-14.053491742346873</v>
+        <v>-13.941929331395183</v>
       </c>
       <c r="B76">
-        <v>3.5199584514967746</v>
+        <v>3.9042036820779868</v>
       </c>
       <c r="C76">
         <v>245.30998079303629</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-15.202474089665524</v>
+        <v>-15.09022064095355</v>
       </c>
       <c r="B77">
-        <v>3.863001237738672</v>
+        <v>4.2502409384066011</v>
       </c>
       <c r="C77">
         <v>245.30998079303629</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-16.349543814279009</v>
+        <v>-16.237544545159849</v>
       </c>
       <c r="B78">
-        <v>4.2122461731358056</v>
+        <v>4.5992674901932968</v>
       </c>
       <c r="C78">
         <v>245.30998079303629</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-17.494159496669237</v>
+        <v>-17.383524058981315</v>
       </c>
       <c r="B79">
-        <v>4.5694489435313494</v>
+        <v>4.95244822622417</v>
       </c>
       <c r="C79">
         <v>245.30998079303629</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-18.635371505097314</v>
+        <v>-18.527497864394643</v>
       </c>
       <c r="B80">
-        <v>4.9376889632140175</v>
+        <v>5.3118266280234794</v>
       </c>
       <c r="C80">
         <v>245.30998079303629</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-19.770848249883105</v>
+        <v>-19.667842033911366</v>
       </c>
       <c r="B81">
-        <v>5.3245269847179708</v>
+        <v>5.6824206532189523</v>
       </c>
       <c r="C81">
         <v>245.30998079303629</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-20.858612944174688</v>
+        <v>-20.775317333651994</v>
       </c>
       <c r="B82">
-        <v>5.8660830553534211</v>
+        <v>6.1545799250034525</v>
       </c>
       <c r="C82">
         <v>245.30998079303629</v>
